--- a/build/filters/questions-2026-08-17/Filters-and-Schedule_Questions-for-Branko_2026-08-17.xlsx
+++ b/build/filters/questions-2026-08-17/Filters-and-Schedule_Questions-for-Branko_2026-08-17.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,8 @@
     <row r="2" ht="150" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hello Branko - this is everything we have open across your projects FILTERS and SCHEDULE after the big filter redesign, gathered into one place so you can answer it in one sitting instead of a trickle of separate messages. Just THREE questions - about ten minutes. SHORT ANSWERS ARE PERFECT - a letter, or one line. Nothing here needs an essay.
+          <t>Hello Branko - this is everything we have open across your projects FILTERS and SCHEDULE, gathered into one place so you can answer it in one sitting instead of a trickle of separate messages. SHORT ANSWERS ARE PERFECT - a letter, or one line. Nothing here needs an essay.
+There are EIGHT questions in total. The first THREE (1 to 3) are the ones we already sent you - they are repeated here only so everything is in one place. Questions 4 to 8 are NEW FOLLOW-UPS, all about the Schedule's 'carryover' feature and one scheduling preference from the design review - so if you have already answered 1 to 3, you only need to look at 4 to 8.
 Every question says which project and screen it is about, because you look after Filters, Schedule and Global Search. Each one is a point where two of your own documents disagree, or where your written description does not yet say the thing we need - so we are asking you which to keep, rather than guessing. To be clear: we have not edited any of your tickets or descriptions.
 The first question has two tests parked on it right now, so it is the one that unblocks work.</t>
         </is>
@@ -467,7 +468,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Three questions - please answer A / B / C or one line.</t>
+          <t>Eight questions - 1 to 3 already sent; 4 to 8 are new follow-ups. Please answer A / B / C or one line.</t>
         </is>
       </c>
     </row>
@@ -594,6 +595,155 @@
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="320" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>SCHEDULE - the scheduling pop-up - a personal 'always schedule the whole work order' preference</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>When you drag a work order onto the schedule, it asks whether to schedule the WHOLE work order or to pick individual lines. Right now it asks this every time.
+The 5 August design review suggested letting each person set a preference - 'always schedule the whole work order' - so the system remembers their choice and stops asking every time.
+Your newer written description does not mention this preference at all, and the review itself listed it as an open question to decide before launch. So we are asking you rather than guessing.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Should a person be able to set a preference to always schedule the whole work order (so the system remembers it and stops asking each time), in the first version?</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>A) YES - add the 'always schedule the whole work order' preference in the first version.
+B) NO - leave it out for now and keep asking each time; maybe a later version.
+C) Something else - please describe it.</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="320" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>SCHEDULE - the schedule grid - the one-click carryover button</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>The old scheduler had a one-click 'carryover' button on a scheduled job. Pressing it copied that job to the next day at the same time.
+The new scheduler does not have this button. The 5 August design review asked to bring it back for the first version.
+Your newer written description does not mention carryover at all, so we are asking you rather than guessing.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Should the one-click carryover button - copy a job to the next day at the same time - be brought back in the first version?</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>A) YES - bring the carryover button back in the first version.
+B) NO - leave it out for now.
+C) Something else - please describe it.</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="320" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>SCHEDULE - the schedule grid - what the carryover button is called</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>This one is only about what the button is CALLED, if it comes back (see the previous question).
+The old name was 'Carryover'. The design review suggested a clearer name - 'Add a Day' or 'Extend a Day' - but the final wording is not decided.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>If the button comes back, what should it be called?</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>A) 'Add a Day'
+B) 'Extend a Day'
+C) Keep 'Carryover', or something else - please write the exact words you want.</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="320" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>SCHEDULE - the schedule grid - carryover on a job that runs several days</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Some jobs are scheduled across several days in a row.
+When you press carryover on one of these, there are two ways it could behave: it could add just ONE more day at the end, or it could copy the whole run of days again.
+The design review said it should add just one more day. Your newer written description does not cover this, so we are checking with you.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>When you press carryover on a job that already runs across several days, should it add just one more day, or copy the whole run of days again?</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>A) Add just ONE more day at the end.
+B) Copy the whole run of days again.
+C) Something else - please describe it.</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13" ht="320" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>SCHEDULE - the schedule grid - week view - dragging a job to the next day</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>In week view you can see several days at once.
+The design review suggested that - as well as, or instead of, a carryover button - a person should be able to drag a scheduled job straight onto the next day.
+Your newer written description does not mention this, so it is your call.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>In week view, should a person be able to drag a scheduled job straight onto the next day, as another way to carry it over?</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>A) YES - allow dragging a job onto the next day in week view.
+B) NO - keep a carryover button as the only way.
+C) Something else - please describe it.</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -606,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -794,38 +944,255 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>4 (NEW)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Schedule: a user-level 'always schedule the whole work order' preference so the scope picker remembers the choice and stops asking each time.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>aug5-review-2026-08-17/RECONCILIATION.md E6 (DIVERGENCE / PO-Q; OUTSTANDING item 2). The Aug-5 review lists it as an open question to decide before V1; Schedule spec v30 is SILENT (0 hits).</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>None - no V1 case authored (spec v30 silent; Rule 58 - not authored from silence).</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Aug-5 design review E6 ('Yes - open question') vs Schedule spec Confluence v30 (13 Aug 2026) - silent on a whole-WO preference. Newer v30 wins (Rule 32); the review item is unratified.</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>A -&gt; author one case for the preference per his answer. B -&gt; confirm dropped for V1 (no case; close the review item). C -&gt; re-scope on his answer.</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>HONESTY AND METHOD NOTES</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>5 (NEW)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Schedule: restore the one-click carryover button (duplicates a scheduled block to the next day at the same time).</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>RECONCILIATION.md E15 (was bug B3; DIVERGENCE / PO-Q; OUTSTANDING item 1). Spec v30 SILENT on carryover entirely (0 hits).</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>None - no V1 case authored (spec v30 silent; Rule 58).</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Aug-5 review E15 ('Yes') vs Schedule spec v30 - no mention of carryover / add-a-day / extend. Rule 32 - v30 wins; Rule 58 - not authored from silence.</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>A -&gt; author carryover-button case(s). B -&gt; confirm dropped; close the item. C -&gt; re-scope.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>HELD, NOT SENT (Standing Rule 66): the question sheet is the LAST thing sent, on the QA lead's word, once everything we can do ourselves on Filters and Schedule is finished. Nothing on this sheet has been written to TestRail or Jira.</t>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>6 (NEW)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Schedule: rename 'Carryover' to 'Add a Day' / 'Extend a Day' (final wording TBC).</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>RECONCILIATION.md E7 (DIVERGENCE / PO-Q; OUTSTANDING item 1). Spec v30 SILENT.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>None - depends on E15 (Q5); no case authored (Rule 58).</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Aug-5 review E7 ('Yes - TBC') vs spec v30 silent. Label decision only; contingent on the carryover button (Q5) existing.</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>A / B -&gt; the chosen label is used when authoring the carryover case. C -&gt; use his exact words.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>FEWEST QUESTIONS (task instruction): only genuine PRODUCT DECISIONS for the PO are on this sheet - never bugs (Rule 7). Bugs/defects go to dev tickets, not to Branko.</t>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>7 (NEW)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Schedule: for a multi-day shift, carryover should add ONE more day, not duplicate the whole span.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>RECONCILIATION.md E8 (DIVERGENCE / PO-Q; OUTSTANDING item 1). Spec v30 SILENT.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>None - depends on E15 (Q5); no case authored (Rule 58).</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Aug-5 review E8 ('Yes' - extend one day) vs spec v30 silent on carryover behaviour.</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>A -&gt; author the carryover case to add exactly one day. B -&gt; whole-span duplicate. C -&gt; re-scope.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>SOURCE CURRENCY (Rule 31): the three items were reconciled against Filters spec Confluence v21 (14 Aug 2026) and Schedule spec Confluence v30 during the 2026-08-17 Fabian-review passes. THIS GENERATOR MADE NO LIVE CONFLUENCE READ - it consolidates already-established open items and the sheet is HELD. OWED BEFORE SENDING (Rule 59): re-read both live spec versions and each question's anchor immediately before the send, and re-verify none has been answered by a spec edit in the meantime.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>DELIBERATELY NOT ON THIS SHEET: (a) the Schedule shop-closures / multi-day-spread contradiction - ANSWERED by spec v30 (skip weekends only, closures receive shifts); cases already follow v30, so it is not a Branko question. (b) The greyed-vs-hidden question is the ONLY Filters tab-behaviour item still open - everything else the redesign changed is settled by spec v21. (c) No open Global Search product decision was found in the current passes.</t>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>8 (NEW)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Schedule: allow dragging a shift onto the next day directly in week view, as an alternative to the carryover button.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>RECONCILIATION.md E9 (DIVERGENCE / PO-Q; OUTSTANDING item 1). Spec v30 SILENT on week-view cross-day drag as carryover (reassignment across tech rows IS covered separately).</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>None - no V1 case for week-view carryover-by-drag. Reassignment across tech rows is covered by SCH-REAS-01 = C30052 (adjacent, not the same behaviour). Rule 58.</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30052 (adjacent - drag reassign across tech rows, not cross-day carryover)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Aug-5 review E9 ('Yes') vs spec v30 - week-view cross-day drag is not a v30 requirement.</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>A -&gt; author a week-view drag-to-next-day case. B -&gt; carryover button only. C -&gt; re-scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>HONESTY AND METHOD NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SEND STATUS: questions 1 to 3 were SENT to Branko on 2026-08-17 (per the QA lead). Questions 4 to 8 are NEW FOLLOW-UPS added 2026-08-18 and are HELD pending the QA lead sending them (Standing Rule 66 - the question sheet is the last thing sent). A follow-up-only copy of the five new questions is 'Filters-and-Schedule_Questions-for-Branko_FOLLOW-UP-5_2026-08-17.docx'. Nothing on this sheet has been written to TestRail or Jira.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ONLY PRODUCT DECISIONS (Rule 7): only genuine PRODUCT DECISIONS for the PO are on this sheet - never bugs. Bugs/defects go to dev tickets, not to Branko.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>FOLLOW-UPS ADDED 2026-08-18 (questions 4-8): the five Schedule carryover / whole-WO-preference items (E6, E15, E7, E8, E9) that the 5 August design review marked V1 but Schedule spec v30 (13 Aug 2026) is SILENT on. Source: build/schedule/aug5-review-2026-08-17/RECONCILIATION.md (OUTSTANDING items 1-2) + build/OUTSTANDING-ITEMS-REGISTER.md (Schedule / Branko, rows SCH-A5-1..5). Not authored from silence (Rule 58); Branko's decision is what unblocks authoring. Also tracked: whichever way he answers, only the QA lead sends the sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SOURCE CURRENCY (Rule 31): the eight items were reconciled against Filters spec Confluence v21 (14 Aug 2026) and Schedule spec Confluence v30 (13 Aug 2026) during the 2026-08-17 Fabian-review and 2026-08-18 Aug-5-review passes. THIS GENERATOR MADE NO LIVE CONFLUENCE READ - it consolidates already-established open items and the follow-ups are HELD. OWED BEFORE SENDING (Rule 59): re-read both live spec versions and each question's anchor immediately before the send, and re-verify none has been answered by a spec edit in the meantime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>DELIBERATELY NOT ON THIS SHEET: (a) the Schedule shop-closures / multi-day-spread contradiction - ANSWERED by spec v30 (skip weekends only, closures receive shifts); cases already follow v30, so it is not a Branko question. (b) The greyed-vs-hidden question is the ONLY Filters tab-behaviour item still open - everything else the redesign changed is settled by spec v21. (c) Aug-5 review items already covered by spec v30 (E1-E5, E10-E12) or confirmed out-of-scope (E13, E14, E16) are not questions - only the 5 divergences v30 is silent on are asked. (d) No open Global Search product decision was found in the current passes.</t>
         </is>
       </c>
     </row>
